--- a/test.xlsx
+++ b/test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prg\myProjects\GitHub\YahooXL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BD5797-5342-4ADC-A31A-73F8EA85C685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C6C75F-265B-49BE-AB10-0E5357D2AB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2180" yWindow="6380" windowWidth="28790" windowHeight="14110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1886" yWindow="1886" windowWidth="24685" windowHeight="13594" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Example" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -299,1175 +300,1207 @@
 <file path=xl/volatileDependencies.xml><?xml version="1.0" encoding="utf-8"?>
 <volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <volType type="realTimeData">
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>675e076c-d470-444e-a1b6-9763cb3b3144</stp>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>d0df84f7-ea54-460a-b8f1-314a8409649a</stp>
+        <tr r="D18" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e0f905e9-a8a4-486d-ac0c-0cee443860c6</stp>
+        <tr r="F8" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>ad49d46c-5e47-4fb6-bbda-309d4f6cd6bf</stp>
+        <tr r="C85" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>b68e2733-f336-4ea0-9ecc-49e0cc7029be</stp>
+        <tr r="C72" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>5e36aa47-3801-44bd-9875-7ca5f6961f65</stp>
+        <tr r="C45" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>8fc0e7e1-4db4-4533-8828-93f68b34fb57</stp>
+        <tr r="C93" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>64a1efdb-0003-4120-b967-6d1a10ccef88</stp>
+        <tr r="C61" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>c789d427-d6ad-4c54-862b-883c38c887f7</stp>
+        <tr r="C100" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>d2ff9022-cddc-405c-8e0b-1b48209496b5</stp>
+        <tr r="J8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>f7da8aaf-45a5-429f-9d2c-b81bea63e9ae</stp>
+        <tr r="D5" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>45bd6f09-6085-4521-b551-63b0c510c107</stp>
         <tr r="B3" s="2"/>
       </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f87d70ec-0632-4fa1-87c7-e8c2df29531b</stp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>62ebdb4f-af70-45b3-b1cc-adc0367d6e19</stp>
+        <tr r="G4" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>064eb10f-a088-4442-afc9-430a00503a60</stp>
+        <tr r="C27" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e78a12ef-cf30-4eaf-ab6f-d55afea9d38d</stp>
+        <tr r="C52" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>dc640f31-8ee0-4ef9-b78a-8fc0a64dc817</stp>
+        <tr r="C15" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>977b3306-28f0-4ca1-b840-363c97190f44</stp>
+        <tr r="D14" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bc397e5e-bc71-45b7-9f64-5b23ccf3803f</stp>
+        <tr r="C68" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>563c8cad-dba0-413a-8e06-bf3c63cd6ac5</stp>
+        <tr r="C86" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>1f50e339-4d0c-44cd-9443-8b889804286f</stp>
+        <tr r="J6" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>2940329d-0a7a-4a49-a338-958103f09dfa</stp>
+        <tr r="K8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>5352f7dc-3338-4d87-9bc0-a74970f9b7bb</stp>
+        <tr r="E8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>a27d3510-43c8-4089-98ec-a27ea99fa7e1</stp>
+        <tr r="I5" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>049d9c48-4b74-4491-8914-e00b8255d2cb</stp>
+        <tr r="C6" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>1c4e278c-7a6f-4e44-aee1-14699a8864ec</stp>
+        <tr r="J4" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>6d35772e-61b6-4a8f-bec4-51aa01a1730f</stp>
+        <tr r="C92" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>fb6f8291-ecf1-4d32-8ee9-84cbf0422574</stp>
+        <tr r="F3" s="2"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>ee8ead2e-3acf-45ad-8ce4-509dcd0c24c3</stp>
+        <tr r="D8" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>80fff4d0-70bc-49fa-8d80-3846d6b507f8</stp>
+        <tr r="C37" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4b20bbf8-7465-4c9f-9356-e453c7bb743b</stp>
+        <tr r="H8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4f74ad1f-291c-4a89-aff9-88b1e02c658a</stp>
+        <tr r="C3" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>478505c3-644b-42dc-af70-83a7fd176ed4</stp>
+        <tr r="C4" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>1e89e4fb-df03-4c15-a5bd-56419dcdebcb</stp>
+        <tr r="D3" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>de9091a0-468f-47ac-bdca-4c385ea914c7</stp>
+        <tr r="C81" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>6d6e655f-3d6c-45e3-a1c9-d2656ed2d73d</stp>
+        <tr r="C51" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>1e4568c3-f7eb-43e6-9ec0-6114749c69ab</stp>
+        <tr r="C38" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>dc94800b-e2ed-40b1-8008-ed0b480b8955</stp>
+        <tr r="I3" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4ca1739c-445e-4721-a66a-7f0d413f9ec3</stp>
+        <tr r="C101" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>b2f6c779-9858-417d-8284-dfdf832a9db2</stp>
+        <tr r="F6" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>74e5259a-0f91-4b06-b609-fc00b266f7bf</stp>
+        <tr r="C89" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e4cbff21-d139-4a51-8ece-3cdebb6f0455</stp>
+        <tr r="I7" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>11db9d3f-751c-4d79-8abe-e8faf4774d4e</stp>
+        <tr r="H3" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>2727c1b4-e7bf-4583-92b5-3566bcdb15cb</stp>
+        <tr r="J7" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4bafcfbf-84ba-473d-988a-ab42da9ea2d9</stp>
+        <tr r="C43" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>91cea746-7f4e-4737-94c6-89f3a9f9a417</stp>
+        <tr r="I6" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>9642b21d-e2e6-48ce-a4da-de684d53b0e2</stp>
+        <tr r="C58" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>c3a62a0b-a145-4a44-a44f-d9905b8f9967</stp>
+        <tr r="C21" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bee39ed9-b42d-49fc-b613-cc54aed53f87</stp>
+        <tr r="F7" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>27f78f0b-914c-4e99-9ed1-0a85c5c0c1be</stp>
+        <tr r="C10" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bd2d7f4e-dad0-47bc-ae15-3166239e8fbb</stp>
+        <tr r="C91" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>27c68767-e8d5-492a-a738-24644a5c52d4</stp>
+        <tr r="C74" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>9ad90596-0ec7-4d4e-b7e4-bc37bacfb987</stp>
+        <tr r="E7" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>1714c32b-648e-4739-9a97-1757584e0bd7</stp>
+        <tr r="B8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>41d32085-c2e8-45ba-bc0d-d0ebaeafb913</stp>
+        <tr r="C44" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4b83464f-b984-4077-ba52-30d75c85d978</stp>
+        <tr r="K3" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>cf945c70-ff36-45a7-a8d5-ee0f529fd92a</stp>
+        <tr r="C83" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>34355d4b-3122-480c-9c10-5867d336ddb3</stp>
+        <tr r="C39" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>3aecf467-fad5-4029-b34b-6ce96b63aa62</stp>
+        <tr r="C49" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>cab778b7-6634-4fdd-8c3f-afa1b2e7f2ff</stp>
+        <tr r="C59" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bc841ac7-8adb-43c2-b9a8-641ad811c8d5</stp>
+        <tr r="C96" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>579930cd-1596-4b94-8676-a261bc6fe847</stp>
+        <tr r="C3" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>f36d4b5c-5c82-4900-8770-a786a988313e</stp>
+        <tr r="B5" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>5039f985-4ca6-4253-8d7c-4bf4609da00b</stp>
+        <tr r="D5" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>cf7bf61c-3244-42d6-a7f3-e8ed526f2b4a</stp>
+        <tr r="C4" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>8d311888-10dd-441c-9821-624e74765a3d</stp>
+        <tr r="C41" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>61bd9952-1a82-4394-83af-4ca3471f0c21</stp>
+        <tr r="H6" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>9fbfb624-e974-4546-bc67-f9436b21e41c</stp>
+        <tr r="J3" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>7c34c5dc-18f9-47b8-84a0-f03ede96a128</stp>
+        <tr r="G8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>2ba03102-8884-44d2-a87d-374cf545868c</stp>
+        <tr r="C62" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>ab86d57c-c9e9-4d23-93a8-0659a9bd005d</stp>
+        <tr r="C14" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>fd450ed1-3720-47a8-93da-dda2bd95075f</stp>
+        <tr r="C78" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>81b9c8a3-34b4-4d96-8cfa-cb8e5b63431f</stp>
+        <tr r="C73" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e0c7e93a-416c-4a27-9473-214c9c62a663</stp>
+        <tr r="D4" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>a2b6e836-2f3d-430a-9bde-fa0d87b342ef</stp>
+        <tr r="K4" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>c8e973a6-0263-4c73-820c-2f97a066c78e</stp>
+        <tr r="C88" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>d2a1dd0c-2f13-4fc8-af37-d9fb49da4686</stp>
+        <tr r="F4" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>c52c262a-b091-48a6-9930-886ff124742d</stp>
+        <tr r="C42" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>82d0a6d9-29e7-4e79-8289-f9fd25f15b24</stp>
+        <tr r="I8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>cb775c68-e076-4d9a-bb01-a95846ad8ce3</stp>
+        <tr r="C46" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>38887a69-e1fe-44a3-a4a8-161733f20377</stp>
+        <tr r="C17" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>5fb14e8a-5371-47f4-836a-3f6fd3bda985</stp>
+        <tr r="C70" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>35ee9964-9dfb-4e99-9ce8-d662ceefcbb6</stp>
+        <tr r="C12" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>36325332-b6ea-4aff-b5bc-08c800ca83dc</stp>
+        <tr r="J5" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>77535c83-fa86-47d4-8f3b-4cc6bcee82b7</stp>
+        <tr r="C95" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e0b308a0-8dc5-4a90-be25-be817bf842df</stp>
+        <tr r="E6" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>8fc653e6-0bb1-45c2-87fc-7ced21341d7f</stp>
+        <tr r="B7" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>da3bac73-d5ad-4e5a-b5ba-b4e23aa99739</stp>
+        <tr r="C8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>083a028e-e531-463d-92ed-295b91302ad6</stp>
+        <tr r="B4" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>3f87e276-a2d2-48d7-b653-8d51fa6014c1</stp>
+        <tr r="D7" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bfc55766-713a-4f01-a7fe-ee79c741ded0</stp>
+        <tr r="F5" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>5dadac34-185f-4731-99a4-ad70ba4f2e85</stp>
+        <tr r="C71" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>36f9ed5b-0642-4deb-95de-ee60cff40a04</stp>
+        <tr r="C8" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>7efcbf7f-a898-4e9e-8876-526b9f339bf0</stp>
+        <tr r="C69" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>10fe0c58-842f-49bd-8640-a636939968ac</stp>
+        <tr r="C80" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>192a5bcb-0f7e-40c1-8dff-ff56deeb6973</stp>
+        <tr r="C22" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>fb4fc709-fb1f-4fcb-ae93-a8644b6ae4f0</stp>
+        <tr r="C2" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>abebd12a-e3d2-4c13-b5e2-15d6512c2b02</stp>
+        <tr r="C7" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>c0e7d9c4-6abb-407b-a17e-4558a9c6bc8c</stp>
+        <tr r="E3" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>618f1c97-554b-46b1-93b6-f672a0dd474c</stp>
+        <tr r="B6" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>8157d596-0eec-414b-a4d6-1764ffaf5f5e</stp>
+        <tr r="C11" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4d43f481-8152-4eb4-addb-68c4c565f037</stp>
+        <tr r="C54" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bcb11340-2739-435f-bded-67bf554cdfe4</stp>
+        <tr r="C97" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>8d6823b1-2a31-4fbf-9f6b-c60f2e421cc5</stp>
+        <tr r="D6" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>fa5e61ad-4a34-41a3-a1c7-c6af7dd08bc4</stp>
+        <tr r="E5" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>058f09ee-420f-4c6c-9238-c0dffdb5a830</stp>
+        <tr r="C24" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>9f350535-5974-4eb1-a20b-37670d99c076</stp>
+        <tr r="C36" s="1"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>4a056b97-a738-4b3f-aed6-8fe28dd6af60</stp>
+        <tr r="D9" s="3"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>6d014f97-a631-4b4f-b15f-8b66c5fa5c49</stp>
+        <tr r="C5" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>ca743325-8698-4fa9-82a9-fcfb4cf0f617</stp>
+        <tr r="C55" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>01cd8dfd-31d5-4cc8-86ec-291ac67070fc</stp>
+        <tr r="D8" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>2b12a608-ccb2-48c3-8ac0-5c5a94af8459</stp>
+        <tr r="C47" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>0371e5d4-b80e-47ec-8b6d-f7f38d700a8b</stp>
+        <tr r="C77" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4c491512-09cb-43d2-9124-5ed7382e98d7</stp>
+        <tr r="H7" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>fcda0404-a772-45ff-a229-ab3771ea2256</stp>
+        <tr r="E4" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>3b45be64-b6a0-4306-b9ee-a202f344a4c9</stp>
+        <tr r="C34" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>5e432b9d-c7ab-4bee-a70a-f8ef78dd2319</stp>
+        <tr r="H5" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e920ce96-2088-424f-bbb3-88f8423dbbc9</stp>
+        <tr r="D15" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bd9ff7c2-21a3-4605-bc1d-d3501bdd26a2</stp>
+        <tr r="C19" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>7a66792a-4745-40df-973f-748325426950</stp>
+        <tr r="C29" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>2cc85322-8433-4f4d-80c9-492024145c27</stp>
+        <tr r="C98" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>13f1768c-d356-48fb-9c35-4e43fa1d7583</stp>
+        <tr r="G6" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>f224f718-e725-46e0-9a26-071f46f79b60</stp>
+        <tr r="C33" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>01f870a4-2896-418d-9d4a-ec9d995a9835</stp>
+        <tr r="C18" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>00f08654-d842-49eb-b107-5d888c128643</stp>
+        <tr r="C57" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>836f4a18-4897-4602-afc1-ed4f0785ce8a</stp>
         <tr r="C94" s="1"/>
       </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>e91a8f95-8072-4fcc-9316-a454a7e551c3</stp>
-        <tr r="D7" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>3e65c417-f422-4837-9bbe-c3127d9982ac</stp>
-        <tr r="B8" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>cddccad4-87a5-46a9-8555-70c71467d24b</stp>
-        <tr r="C15" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>5a357039-6a5a-4c51-bc6d-5c07a59f21e2</stp>
-        <tr r="I3" s="2"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>e6c53cac-0782-48e3-b268-c3d73672ab50</stp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>09a82ccc-8dfe-46bb-b478-870cdbd39c04</stp>
+        <tr r="C32" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4b7935aa-ecde-4f47-8ae3-739c33b5dae4</stp>
+        <tr r="C7" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>71c7d47b-0791-46b6-84ef-aafb26aab066</stp>
+        <tr r="C50" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>eb7bd034-dea3-4234-8753-4e5c5f1705c4</stp>
+        <tr r="H4" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>6250a736-18e4-4356-8771-227ee3e92439</stp>
+        <tr r="C53" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>fbe2c046-0313-4694-8968-faa39ebf4d76</stp>
+        <tr r="C66" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>a22795fc-fb55-47c3-93a8-b12e5abbec37</stp>
+        <tr r="C87" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>89d97826-cba7-42e2-ac01-ece3da501b0b</stp>
+        <tr r="C99" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>3bd972c2-945a-47e0-a991-b11e3bd4b34f</stp>
+        <tr r="C9" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>25db10e2-31bd-4822-8f29-644b51b4d3aa</stp>
+        <tr r="C5" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>dec2d36f-dcc4-4a17-af64-b1e36aac0c8a</stp>
+        <tr r="C75" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>5fbaf62d-6b2b-4769-9c90-6e56df852e83</stp>
+        <tr r="C30" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e4b7d4f9-582c-40bc-bf7c-665dfaa909ef</stp>
+        <tr r="C79" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>3e946431-d1ef-4a18-a515-8d5c7dfb4318</stp>
+        <tr r="C6" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>f2b6645f-ec71-409b-abf6-96281f7ce8fb</stp>
+        <tr r="C60" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>73f620b7-e22f-4fe6-b68b-b611ae1144fd</stp>
+        <tr r="D12" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>3baf0391-f050-4785-b0d8-8afa38aff0fd</stp>
+        <tr r="C65" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>409104bd-9b34-4103-984a-cc486a64a643</stp>
+        <tr r="C16" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>93121763-dfee-423d-b996-26298cfa5fec</stp>
+        <tr r="C67" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e4a29719-7897-4d69-94be-6d3a669f23d8</stp>
+        <tr r="C35" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>71fa5a2d-c929-4757-9e3b-19d58f1f5fb6</stp>
+        <tr r="C84" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>3fd94831-4beb-4a30-ac4a-a52b03e86f56</stp>
+        <tr r="C48" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>9b9724e6-95f2-4759-b3c2-af281feb18a4</stp>
+        <tr r="C26" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>6c882fc1-860a-4b48-8a1a-b277c3ffa85a</stp>
+        <tr r="C102" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>0fa9a62e-9c98-4877-ad00-faac6f36cd6f</stp>
+        <tr r="C63" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>18af38d7-bee2-450f-a91e-78789b07cb91</stp>
+        <tr r="C76" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>ab8e0b64-e117-40db-a593-6d98835edd97</stp>
+        <tr r="I4" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>1d03a191-d2c0-4f6e-b2a9-a98e0a25bac2</stp>
+        <tr r="G3" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>f57a60dc-0f12-4cd1-8c87-4979d1b6e83d</stp>
+        <tr r="C64" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>9df06c51-27ee-43f4-8541-3f7e59a4ff99</stp>
+        <tr r="C20" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>8fae5616-fc37-41bf-b491-e046c1016d66</stp>
+        <tr r="D13" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>565a27d2-9569-49d4-bc35-ef9be7158e60</stp>
+        <tr r="C56" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>b9159a51-3907-467b-837d-bca0ad4612f5</stp>
+        <tr r="D21" s="3"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e65ce15c-adec-4933-aba7-80467962e654</stp>
+        <tr r="G5" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>1fa9113a-e347-4ab9-9274-5da5a0a3bc51</stp>
+        <tr r="D19" s="3"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>4c8ef173-66a7-4593-8982-4ea84678a63a</stp>
+        <tr r="C90" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>7b4e7362-ab9e-4f4e-91d7-75d546f0b889</stp>
+        <tr r="C82" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bd6cdf18-7044-45ee-b0bd-e9b92e7c7dbf</stp>
+        <tr r="K7" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bece6fa8-43e0-4089-a225-944676a2b424</stp>
+        <tr r="C25" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>93545d13-ab58-4bff-8242-c9c23c50342f</stp>
+        <tr r="K6" s="2"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>739e22a9-d05b-4fe9-b461-0c1aad7bdd6b</stp>
+        <tr r="K5" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>7860c354-332d-44c5-b5db-93b3ef58c5bd</stp>
+        <tr r="C31" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>ad23ef53-2622-4f02-95ee-6e855844d397</stp>
+        <tr r="G7" s="2"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>bf554a63-0759-4b78-8555-e2434e783d43</stp>
+        <tr r="C40" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>8b9f8e89-af5b-4dfb-a020-ac206dc6298e</stp>
+        <tr r="D2" s="3"/>
         <tr r="D3" s="3"/>
-        <tr r="D2" s="3"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>57cd6ac6-b0b4-48c2-83b3-04355c23b555</stp>
-        <tr r="B7" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f6e97d91-d231-4747-9d63-1a3c0be40294</stp>
-        <tr r="C74" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>71538457-7cec-43af-8545-4e05e590c6ac</stp>
-        <tr r="H7" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f87300f2-ede3-4e13-a431-7011c9e5bb42</stp>
-        <tr r="C52" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>4081f021-a35b-4fb5-85b8-f120a30302b1</stp>
-        <tr r="C99" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>4458af14-82a1-4a58-b2b3-e1ac6b82af94</stp>
-        <tr r="D15" s="3"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>29d70fae-d2db-4719-9bfb-8a9d3896b83f</stp>
-        <tr r="C39" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>b06899db-d778-4cb6-b1c5-d9beb4d5b009</stp>
-        <tr r="C2" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>08cb8ce9-413f-4585-a260-15262de8b837</stp>
-        <tr r="G4" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>51d6ccb0-8bff-4469-a420-a3d72dda839b</stp>
-        <tr r="C92" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>13ecedb4-d61a-41b0-9696-060540a6e8ba</stp>
-        <tr r="C50" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>b4b1dd36-404b-4a60-8b6d-20bdfc2245c1</stp>
-        <tr r="G8" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>30f3b17b-9675-4830-b26b-d5cd58e7b75f</stp>
-        <tr r="D5" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>986533d6-951e-4bfb-81f8-ec3c33428bf9</stp>
-        <tr r="H8" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d56471ee-f0cb-4992-bbb6-5be3ca8d1571</stp>
-        <tr r="D19" s="3"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>48999476-a602-4637-819a-f52d5be13074</stp>
-        <tr r="K8" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9d277ef1-a8e7-4f3e-9fd9-531852949d9a</stp>
-        <tr r="I4" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9208d694-d83b-4fca-964e-904f8c5f2b09</stp>
-        <tr r="J4" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>013e9ce7-f17f-4c17-9e44-5ddb6ee3620c</stp>
-        <tr r="D3" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>cf29a910-3192-4738-b931-4aa91f34ad35</stp>
-        <tr r="C40" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>ef967352-78eb-4314-b027-8f5c40694162</stp>
-        <tr r="F5" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>1eef8984-5318-42bd-8009-ec9548ae5e72</stp>
-        <tr r="C3" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9fbc87dc-bf9b-46fa-9a7b-a45bf24dca17</stp>
-        <tr r="E6" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>47986555-c93f-4fec-9cbb-c2b762babb95</stp>
-        <tr r="H4" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>bccf1c0c-a637-447d-9c1c-9a9ce5f70b69</stp>
-        <tr r="J7" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c0e64bc3-ed84-4d4f-a51b-4c7697f235a8</stp>
-        <tr r="C33" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>051c0844-ed4d-4659-aecc-2b09a5240d15</stp>
-        <tr r="C89" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>def6178d-1f02-4933-bc1a-e435b6cf3b80</stp>
-        <tr r="G7" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>07a4a212-ba14-4ad2-9106-0471dc033317</stp>
-        <tr r="E5" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>6e25fabf-2711-47f0-8a43-36dbdd993a5a</stp>
-        <tr r="C30" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c56253ca-63fc-41fb-b30a-31a04ec507bb</stp>
-        <tr r="C8" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c43b78d5-bde0-4103-9984-9ac0d6ae23e5</stp>
-        <tr r="C34" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>125a81ab-da80-4796-83a4-72e32ffcbec1</stp>
-        <tr r="H6" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c9949bbe-03c3-4724-b021-fda509eb9134</stp>
-        <tr r="F7" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>85dc29f4-cb2d-4aac-9898-6a516b26a764</stp>
-        <tr r="C48" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d2072ddc-f268-4b6b-b20f-e96989dafc99</stp>
-        <tr r="C46" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>2dc1732f-75fc-4fb3-930a-f708ff08a277</stp>
-        <tr r="C65" s="1"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>3289290c-9983-48fa-b138-5a055b2ebc73</stp>
-        <tr r="H15" s="3"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>5393f28a-b67f-4bcd-9e11-8379636b469f</stp>
-        <tr r="C22" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d96d2ab9-2493-4685-bb9d-98329f95d843</stp>
-        <tr r="C37" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>404f36e0-c62a-4948-90cc-8105a77f68a1</stp>
-        <tr r="C86" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>cc318681-798b-4a14-9e90-ab9f441dd66c</stp>
-        <tr r="C60" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c7271251-b1c2-4d8d-96de-3aad8103c887</stp>
-        <tr r="C41" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>b2d6c7ad-ef60-4a2e-918a-215977b3143f</stp>
-        <tr r="C64" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>bfeaacf1-98b3-4a25-a845-444b556d8295</stp>
-        <tr r="C97" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>3d6f48de-491e-4ccf-8f4a-412c0f64ac97</stp>
-        <tr r="C54" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>7b4b8203-b6b2-4154-9499-aea6319e0ecc</stp>
-        <tr r="C3" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>cb50e198-7d08-4e60-a3ba-914840615991</stp>
-        <tr r="C6" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>465e1111-3490-4d68-b029-40daf0caf00d</stp>
-        <tr r="C11" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>0a3d6a82-d88b-4519-8b30-9f66957bd387</stp>
-        <tr r="C44" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>192c2a78-a0de-43f7-8664-acbcdd3d214d</stp>
-        <tr r="C95" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>e7a1bb2a-91a1-4a24-a606-4f07ce470e5a</stp>
-        <tr r="C38" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>bb282c49-9c93-4b83-9966-0f24b33f6f12</stp>
-        <tr r="C69" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d4c37905-ba7f-4d40-943e-26cc919deeba</stp>
-        <tr r="B6" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>065e63ff-1231-45f7-a149-02dc08410037</stp>
-        <tr r="C82" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>b473f0e9-9ec4-4b94-9a2a-3183bc1bedd9</stp>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>0dd8fae0-cc32-4161-9365-3ba2e385c857</stp>
         <tr r="C28" s="1"/>
       </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>5d6d0fca-1e9a-432a-b4ab-7960f62d712a</stp>
-        <tr r="C72" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c5e73f72-5aa7-4db8-9c5e-20587b433414</stp>
-        <tr r="C4" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>1bc262c1-8ff1-4f92-b3a9-b1d8ceeadb0c</stp>
-        <tr r="C14" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>cd21c811-c0ed-4ca3-9c09-c13861a9e12f</stp>
-        <tr r="D6" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d1fafe79-4365-4fd8-8358-8f1b36575046</stp>
-        <tr r="G3" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c095c570-84e1-43ef-9393-e9f63dcab388</stp>
+    </main>
+    <main first="rtdsrv_14a128f30c344e0aa834261d5904b48b">
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>c0d1cacc-5636-4035-8c5f-88e180900d38</stp>
+        <tr r="C13" s="1"/>
+      </tp>
+      <tp>
+        <v>9</v>
+        <stp/>
+        <stp>e7a2a119-2a6a-4956-959f-ad67b6e2fa33</stp>
         <tr r="C23" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>18ae126e-d3d1-4d4f-92b9-aa38d1b63651</stp>
-        <tr r="C96" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>2bc726f3-1752-4d4b-ad93-d37a1d190b7b</stp>
-        <tr r="C29" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>fec9fe0c-bcd2-4519-b602-5714bfe3a1dd</stp>
-        <tr r="C91" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>8a9463b6-ae99-4ba9-a5e3-ca28801b353e</stp>
-        <tr r="K6" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>4aa45c9f-4ab2-452e-98af-380bfd63aef3</stp>
-        <tr r="C73" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>eeb545f6-37b1-4878-8e31-4f1a0cf32f0c</stp>
-        <tr r="K3" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>6f54bd74-b112-4e58-86b6-8e7f81f94e50</stp>
-        <tr r="C83" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>6a465c9c-1318-44e4-80e5-68c5dd8d5535</stp>
-        <tr r="F8" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c172e820-713b-4096-ae92-68c1f49c166c</stp>
-        <tr r="C17" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>da73336a-8acf-405e-94c0-30d5e38abe09</stp>
-        <tr r="C57" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>30485f29-9e03-43d6-8fa4-238d87eae644</stp>
-        <tr r="F4" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>4d35dfb3-c5be-437d-a600-e6264834f131</stp>
-        <tr r="C24" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d1231e66-3a1f-403d-b983-c4f7b45221e6</stp>
-        <tr r="C100" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d4996723-7301-4780-b45c-0adddc9e09d4</stp>
-        <tr r="C78" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>11a0b5ba-a336-4ada-98d9-7993a2244aaf</stp>
-        <tr r="C102" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>fab54e58-6770-45b7-8598-cbde2cbc84eb</stp>
-        <tr r="C79" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>6793bb13-7aaf-4b77-9815-5340cf8ab860</stp>
-        <tr r="J5" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>30f93b2e-53f8-4540-bb6f-7929a4fe0e59</stp>
-        <tr r="C10" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9c1665d3-7e94-4ee8-ac7e-66f374968ef8</stp>
-        <tr r="C45" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>b3af8d5c-99d1-44ea-95aa-25de3d4ad67b</stp>
-        <tr r="C58" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>05c4c6ce-d3f4-45f9-8667-065b7e773325</stp>
-        <tr r="C36" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f0511eec-ed85-4e1c-9944-6b3d058b882c</stp>
-        <tr r="C25" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>77d8922c-f038-4b5a-9f8f-d9a3e3ca88de</stp>
-        <tr r="E4" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>235686c8-7eb7-48ca-9fdf-773dac6984d7</stp>
-        <tr r="C85" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>3d5ee708-ca8e-4b21-89ea-67231559e12a</stp>
-        <tr r="C56" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f52cd4af-09cf-4a14-a8e4-d389abc1bf67</stp>
-        <tr r="G6" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>379fcba0-6f43-4c5a-a824-cceaeec71a31</stp>
-        <tr r="I6" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>4c36e5a6-0517-4901-982e-d08815a127ba</stp>
-        <tr r="E3" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>80945ab4-47a0-4ea5-887a-6cc5e2cceaa1</stp>
-        <tr r="F6" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>50c368ce-8175-4ba7-b793-7b0f088993ca</stp>
-        <tr r="C26" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>1eb635c3-6bc9-4478-8660-052d638d28d4</stp>
-        <tr r="C59" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>542100d8-cc0d-4e10-8e3f-0df36fa6b023</stp>
-        <tr r="K5" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>68b82175-3409-44af-bf2d-fb5fdb83e8ce</stp>
-        <tr r="C47" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f3675236-6ed2-4709-b9b1-b5d80852c465</stp>
-        <tr r="D4" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>a3058153-bbee-42ff-98a3-931df309c239</stp>
-        <tr r="C7" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c50b00d9-4d27-4f5c-8721-1423e37882b4</stp>
-        <tr r="C9" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>ee7dc4c4-0d19-416d-ac7d-d60cdc02e25e</stp>
-        <tr r="C84" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>8a1e9ac6-6f91-4245-8478-f4b5f783fb5e</stp>
-        <tr r="C87" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>5c30586e-a14c-48b0-886d-85aa3de9f9b9</stp>
-        <tr r="C75" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f81eefd8-e4dd-4023-8e9e-66c5506e9cb0</stp>
-        <tr r="J8" s="2"/>
-      </tp>
-      <tp>
-        <v>1391</v>
-        <stp/>
-        <stp>77804990-0161-465b-acad-b988546e3ddc</stp>
-        <tr r="E8" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9e526134-0b49-4f6b-bfe8-3c4922aaef10</stp>
-        <tr r="C70" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>cf43e080-5fe2-4013-953a-7cae60ca2d08</stp>
-        <tr r="C18" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>6e882f9f-6cc9-41a1-b84a-47625ab2522b</stp>
-        <tr r="C5" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f8b251f1-ddaf-4ef1-bc80-92347671e47e</stp>
-        <tr r="C71" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>659baf8d-c2fd-4cef-a9dc-d7357b0ec393</stp>
-        <tr r="I5" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>1ee3cad0-23ec-4182-8537-658d50075a77</stp>
-        <tr r="D12" s="3"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9ccc6133-e7a2-4366-acfc-a3d30d154c28</stp>
-        <tr r="K4" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>0870d5ee-91fe-40b0-b579-60cd5e21b5ad</stp>
-        <tr r="B4" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>5feba4c4-93e1-424a-aa62-35fdfb0599e9</stp>
-        <tr r="C68" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>59594a8c-85bf-42c6-9c6e-240987b0a175</stp>
-        <tr r="C67" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>1bc6f97c-dfe2-4ba1-82e8-58c1b50d2468</stp>
-        <tr r="C19" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>3742e68e-ba99-4c0a-9c6a-abc2323c15c6</stp>
-        <tr r="C51" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f60285ac-b4eb-4af1-a1d8-7ffc505f9368</stp>
-        <tr r="C13" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>a0328227-0b5c-483c-8bc0-cde7fadd6f60</stp>
-        <tr r="C4" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>b899685c-d9aa-42f3-869c-7b1f8d2148ad</stp>
-        <tr r="I7" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>90c061ff-2fef-4320-a0fa-975b1f057d42</stp>
-        <tr r="J6" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>2f79b264-6f43-43ea-9dc1-eefc9c72b644</stp>
-        <tr r="D13" s="3"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>a64a2eea-d8a8-4cc6-9bf2-310dfba14d41</stp>
-        <tr r="C32" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>89a3d8a2-ecc0-46a4-99b9-43646dc9850d</stp>
-        <tr r="C101" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f9fe1289-898d-49f0-8fcb-bd8fac4aa738</stp>
-        <tr r="C6" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>4ed61c95-e1e1-4b46-b946-fd48ddf36124</stp>
-        <tr r="C27" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>14ddfc9a-5636-4a11-bb32-adc462eadf06</stp>
-        <tr r="C81" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>cd606cb2-dca5-49fc-b6ee-49e4d1cfd2ed</stp>
-        <tr r="C16" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>e62a7d0c-e77f-4090-9075-1dd2a37f9881</stp>
-        <tr r="C88" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>bdb3d9ac-ed25-4743-8911-d3b794837c1e</stp>
-        <tr r="C31" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>731542de-7ce4-49cd-9e95-77097c491a9d</stp>
-        <tr r="C77" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>b87d1e94-b112-4a12-b4ef-afa5232ddc2b</stp>
-        <tr r="C20" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>f68105b9-afa1-4fa9-825d-8e3d90a5be30</stp>
-        <tr r="C8" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>e8b8144e-2529-4bf4-9fd2-402d91fb11b4</stp>
-        <tr r="J3" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>68a39f62-5287-4e3e-8a4e-2d681d403dcf</stp>
-        <tr r="C35" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>1e50e468-d15f-4dd6-a66a-8d67f90de670</stp>
-        <tr r="C12" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>52fe8087-4b54-4808-a0cf-c1713653c445</stp>
-        <tr r="F3" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>730f5916-4680-49f0-96fe-324a6fd16a70</stp>
-        <tr r="C76" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>534059b7-0dd7-4194-b37c-76320fe384a0</stp>
-        <tr r="C49" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>20a61bdf-1269-42fc-a0f9-09f77d293f51</stp>
-        <tr r="K7" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>8c81ef80-fe72-4be9-8235-6c008edd030a</stp>
-        <tr r="D18" s="3"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>498e2d6c-57df-4f9e-9a26-427042240c20</stp>
-        <tr r="G5" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>bcb1357b-ad99-409a-a6ed-7aa696d64869</stp>
-        <tr r="C43" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>10e4aae0-6af2-47a8-a96e-f2a8cf557a6e</stp>
-        <tr r="C53" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>6fa683a4-fa8b-4deb-a2f7-caa8482462e0</stp>
-        <tr r="C93" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>7e595962-f928-40b3-92ed-623e6764158e</stp>
-        <tr r="H3" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>80fe421b-96a2-45a7-b3e3-62ae77cd67cc</stp>
-        <tr r="B5" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9fa38654-b40d-42d8-a147-66b7fb166191</stp>
-        <tr r="I8" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>fb0d4cc8-d2e7-4a65-ad85-7aa087413e80</stp>
-        <tr r="C5" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>59bb33e4-0621-48dc-a5de-0f993d638dba</stp>
-        <tr r="C7" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>d5d0ba5b-7de3-4976-9ef2-820fa9c2ec7d</stp>
-        <tr r="D21" s="3"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>51e60fcf-4730-4ce2-a78f-0f82b2d59fa0</stp>
-        <tr r="C62" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>96a512c3-5a99-4147-9322-a30dd99a7e2c</stp>
-        <tr r="D14" s="3"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c391fe36-093d-484a-89bc-60231938d6a2</stp>
-        <tr r="C55" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c9436c87-f9f9-49b6-bd5d-5be5ac7f1d39</stp>
-        <tr r="C90" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>38fe685c-d34b-4685-aa89-5e6f1e300315</stp>
-        <tr r="D8" s="2"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>7cc02974-1d5e-4ab1-a0a9-42c57b2e7151</stp>
-        <tr r="E8" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>6582141c-f7a1-40c3-8782-021690d3d7f6</stp>
-        <tr r="C98" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>abecf466-d073-43d0-81b3-c8ff547d85b3</stp>
-        <tr r="C42" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>c8724f6c-5de1-4a51-87de-3b5e0ab9dd4d</stp>
-        <tr r="E7" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>9971ac55-87a8-4548-b0f1-655c52ed2cae</stp>
-        <tr r="C66" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>e61aae47-da07-48de-ae27-88b7ae6dee4b</stp>
-        <tr r="C21" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>2df90be9-7281-49a7-8397-fcf93763f32d</stp>
-        <tr r="C63" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>900e63c0-6a14-4028-be6f-7fd0ed44daf7</stp>
-        <tr r="C80" s="1"/>
-      </tp>
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>072f1ac2-75a9-4af9-bc2a-b56a1ea8ab1f</stp>
-        <tr r="H5" s="2"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_c54fba4079374bfda2f728c30f788de8">
-      <tp>
-        <v>46</v>
-        <stp/>
-        <stp>a4b6a926-b314-435f-a6fd-d190267640b5</stp>
-        <tr r="C61" s="1"/>
       </tp>
     </main>
   </volType>
@@ -1771,16 +1804,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE329460-81FC-4BC2-B92D-65FDD83E0350}">
-  <dimension ref="B1:L34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:E34"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="20.6328125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="54.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.23046875" customWidth="1"/>
+    <col min="2" max="2" width="11.84375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="20.61328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="54.61328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1788,25 +1821,25 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" t="str" cm="1">
         <f t="array" ref="D2">_xll.YahooQuote("","")</f>
-        <v>IBXL, Version=0.1.0.0, Culture=neutral, PublicKeyToken=null</v>
+        <v>YahooXL, Version=2.0.0.0, Culture=neutral, PublicKeyToken=null</v>
       </c>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
       <c r="D3" t="str" cm="1">
         <f t="array" ref="D3">_xll.YahooQuote("","")</f>
-        <v>IBXL, Version=0.1.0.0, Culture=neutral, PublicKeyToken=null</v>
+        <v>YahooXL, Version=2.0.0.0, Culture=neutral, PublicKeyToken=null</v>
       </c>
       <c r="E3" s="20"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="16"/>
       <c r="C4" s="15"/>
       <c r="D4" t="str" cm="1">
@@ -1814,17 +1847,17 @@
         <v>YahooXL, Version=1.1.0.0, Culture=neutral, PublicKeyToken=null</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" t="str" cm="1">
         <f t="array" ref="D5">_xll.YahooQuote(B5,C5)</f>
-        <v>C:\prg\myProjects\GitHub\YahooXL\YahooXL\bin\Debug\net8.0-windows\YahooXL-AddIn64.xll</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+        <v>C:\prg\myProjects\GitHub\YahooXL\YahooXL\bin\Debug\net9.0-windows8.0\YahooXL-AddIn64.xll</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="15"/>
       <c r="C6" s="15" t="s">
         <v>25</v>
@@ -1834,7 +1867,7 @@
         <v>LongName</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="15"/>
       <c r="C7" s="15">
         <v>6</v>
@@ -1844,7 +1877,7 @@
         <v>LongName</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="15"/>
       <c r="C8" s="15">
         <v>200</v>
@@ -1853,12 +1886,8 @@
         <f t="array" ref="D8">_xll.YahooQuote(B8,C8)</f>
         <v>#Property name index: 0..100.</v>
       </c>
-      <c r="H8" t="str" cm="1">
-        <f t="array" ref="H8">_xll.IBPositions()</f>
-        <v>IBXL, Version=0.1.0.0, Culture=neutral, PublicKeyToken=null</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="15"/>
       <c r="C9" s="15" t="s">
         <v>22</v>
@@ -1868,7 +1897,7 @@
         <v>#Invalid property name: 'invalid prop'.</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="15" t="s">
         <v>23</v>
       </c>
@@ -1879,12 +1908,8 @@
         <f t="array" ref="D10">_xll.YahooQuote(B10,C10)</f>
         <v>#Invalid property name: 'invalid prop'.</v>
       </c>
-      <c r="H10" t="e" cm="1">
-        <f t="array" ref="H10">_xll.IBPositions("TSLA")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="15" t="s">
         <v>18</v>
       </c>
@@ -1895,12 +1920,8 @@
         <f t="array" ref="D11">_xll.YahooQuote(B11,C11)</f>
         <v>#Invalid property name: 'invalid prop'.</v>
       </c>
-      <c r="H11" t="e" cm="1">
-        <f t="array" ref="H11">_xll.IBPositions("TSLA")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="15" t="s">
         <v>18</v>
       </c>
@@ -1911,12 +1932,8 @@
         <f t="array" ref="D12">_xll.YahooQuote(B12,C12)</f>
         <v>International Business Machines Corporation</v>
       </c>
-      <c r="H12" t="e" cm="1">
-        <f t="array" ref="H12">_xll.IBPositions("TSLA")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="15" t="s">
         <v>29</v>
       </c>
@@ -1928,7 +1945,7 @@
         <v>IBM</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="15" t="s">
         <v>18</v>
       </c>
@@ -1940,33 +1957,17 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="7" cm="1">
         <f t="array" ref="D15">_xll.YahooQuote(B15,C15)</f>
-        <v>208.25</v>
-      </c>
-      <c r="H15" t="str" cm="1">
-        <f t="array" ref="H15:L16">_xll.IBPositions()</f>
-        <v>DU003</v>
-      </c>
-      <c r="I15">
-        <v>444857009</v>
-      </c>
-      <c r="J15" t="str">
-        <v>PLTR</v>
-      </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15">
-        <v>41.930047999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+        <v>284.31</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -1975,23 +1976,8 @@
         <f t="array" ref="D16">_xll.YahooQuote(B16,C16)</f>
         <v>#Invalid symbol name: 'invalid sym'.</v>
       </c>
-      <c r="H16" t="str">
-        <v>DU003</v>
-      </c>
-      <c r="I16">
-        <v>4815747</v>
-      </c>
-      <c r="J16" t="str">
-        <v>NVDA</v>
-      </c>
-      <c r="K16">
-        <v>100</v>
-      </c>
-      <c r="L16">
-        <v>135.41004799999999</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B17" s="15" t="s">
         <v>24</v>
       </c>
@@ -2001,7 +1987,7 @@
         <v>#Symbol not found: 'UNKNOWN'.</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B18" s="15" t="s">
         <v>18</v>
       </c>
@@ -2013,7 +1999,7 @@
         <v>IBM</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
@@ -2025,7 +2011,7 @@
         <v>USD=X</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B20" s="15" t="s">
         <v>27</v>
       </c>
@@ -2035,65 +2021,65 @@
         <v>#Invalid symbol name: 'JPY=X'.</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="7" cm="1">
         <f t="array" ref="D21">_xll.YahooQuote(B21,C21)</f>
-        <v>152.244</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+        <v>149.45400000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
     </row>
@@ -2105,17 +2091,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" customWidth="1"/>
-    <col min="2" max="2" width="31.7265625" customWidth="1"/>
-    <col min="3" max="3" width="49.453125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.54296875" customWidth="1"/>
+    <col min="1" max="1" width="6.23046875" customWidth="1"/>
+    <col min="2" max="2" width="31.69140625" customWidth="1"/>
+    <col min="3" max="3" width="49.4609375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="10.921875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="27.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B1" s="19" t="s">
         <v>16</v>
       </c>
@@ -2126,7 +2112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2143,7 +2129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" ref="A3:A68" si="0">+A2+1</f>
         <v>1</v>
@@ -2161,7 +2147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2179,7 +2165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2204,7 +2190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2229,7 +2215,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2254,7 +2240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2271,15 +2257,15 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E8" t="str" cm="1">
-        <f t="array" ref="E8">_xll.DnaRtdClock()</f>
-        <v>04:13:47</v>
+      <c r="E8" t="e" cm="1">
+        <f t="array" aca="1" ref="E8" ca="1">_xll.DnaRtdClock()</f>
+        <v>#NAME?</v>
       </c>
       <c r="F8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2304,7 +2290,7 @@
         <v>0.81311342592592595</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2323,7 +2309,7 @@
       </c>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2342,7 +2328,7 @@
       </c>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2363,7 +2349,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2381,7 +2367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2399,7 +2385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2417,7 +2403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2435,7 +2421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2453,7 +2439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2471,7 +2457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2489,7 +2475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2507,7 +2493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2525,7 +2511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2543,7 +2529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2561,7 +2547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2579,7 +2565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2597,7 +2583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2615,7 +2601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2626,14 +2612,14 @@
       </c>
       <c r="C27" s="6">
         <f>+_xll.YahooQuote(C$1,$B27)</f>
-        <v>192557318144</v>
+        <v>264840232960</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2644,14 +2630,14 @@
       </c>
       <c r="C28" s="6">
         <f>+_xll.YahooQuote(C$1,$B28)</f>
-        <v>924644992</v>
+        <v>931519242</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2669,7 +2655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2680,14 +2666,14 @@
       </c>
       <c r="C30" s="6">
         <f>+_xll.YahooQuote(C$1,$B30)</f>
-        <v>207.3</v>
+        <v>284.3</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2698,14 +2684,14 @@
       </c>
       <c r="C31" s="6">
         <f>+_xll.YahooQuote(C$1,$B31)</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2716,14 +2702,14 @@
       </c>
       <c r="C32" s="6">
         <f>+_xll.YahooQuote(C$1,$B32)</f>
-        <v>208.7</v>
+        <v>284.85000000000002</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2734,7 +2720,7 @@
       </c>
       <c r="C33" s="6">
         <f>+_xll.YahooQuote(C$1,$B33)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D33" s="6">
         <f t="shared" si="1"/>
@@ -2743,7 +2729,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2754,7 +2740,7 @@
       </c>
       <c r="C34" s="6">
         <f>+_xll.YahooQuote(C$1,$B34)</f>
-        <v>206.72</v>
+        <v>281.44</v>
       </c>
       <c r="D34" s="6">
         <f t="shared" si="1"/>
@@ -2763,7 +2749,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2774,7 +2760,7 @@
       </c>
       <c r="C35" s="6">
         <f>+_xll.YahooQuote(C$1,$B35)</f>
-        <v>207.77</v>
+        <v>280.51</v>
       </c>
       <c r="D35" s="6">
         <f t="shared" si="1"/>
@@ -2783,7 +2769,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2794,7 +2780,7 @@
       </c>
       <c r="C36" s="6">
         <f>+_xll.YahooQuote(C$1,$B36)</f>
-        <v>209.83500000000001</v>
+        <v>288.82</v>
       </c>
       <c r="D36" s="6">
         <f t="shared" si="1"/>
@@ -2803,7 +2789,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2814,14 +2800,14 @@
       </c>
       <c r="C37" s="6">
         <f>+_xll.YahooQuote(C$1,$B37)</f>
-        <v>207.49</v>
+        <v>280.12</v>
       </c>
       <c r="D37" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2832,14 +2818,14 @@
       </c>
       <c r="C38" s="6" t="str">
         <f>+_xll.YahooQuote(C$1,$B38)</f>
-        <v>207.49 - 209.835</v>
+        <v>280.12 - 288.82</v>
       </c>
       <c r="D38" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2850,14 +2836,14 @@
       </c>
       <c r="C39" s="6">
         <f>+_xll.YahooQuote(C$1,$B39)</f>
-        <v>3302804</v>
+        <v>8119844</v>
       </c>
       <c r="D39" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2868,14 +2854,14 @@
       </c>
       <c r="C40" s="6">
         <f>+_xll.YahooQuote(C$1,$B40)</f>
-        <v>5784840</v>
+        <v>5972070</v>
       </c>
       <c r="D40" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2886,14 +2872,14 @@
       </c>
       <c r="C41" s="6">
         <f>+_xll.YahooQuote(C$1,$B41)</f>
-        <v>3894098</v>
+        <v>5013188</v>
       </c>
       <c r="D41" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2904,14 +2890,14 @@
       </c>
       <c r="C42" s="14">
         <f>+_xll.YahooQuote(C$1,$B42)</f>
-        <v>45597.833356481482</v>
+        <v>45926.833356481482</v>
       </c>
       <c r="D42" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2922,14 +2908,14 @@
       </c>
       <c r="C43" s="6">
         <f>+_xll.YahooQuote(C$1,$B43)</f>
-        <v>208.25</v>
+        <v>284.31</v>
       </c>
       <c r="D43" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2940,14 +2926,14 @@
       </c>
       <c r="C44" s="6">
         <f>+_xll.YahooQuote(C$1,$B44)</f>
-        <v>1.53</v>
+        <v>2.87</v>
       </c>
       <c r="D44" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2958,7 +2944,7 @@
       </c>
       <c r="C45" s="6">
         <f>+_xll.YahooQuote(C$1,$B45)</f>
-        <v>0.74013099999999998</v>
+        <v>1.0197499999999999</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" si="1"/>
@@ -2967,7 +2953,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -2987,7 +2973,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3007,7 +2993,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3025,7 +3011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3045,7 +3031,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="9"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3056,14 +3042,14 @@
       </c>
       <c r="C50" s="14">
         <f>+_xll.YahooQuote(C$1,$B50)</f>
-        <v>45598.00277777778</v>
+        <v>45926.999976851854</v>
       </c>
       <c r="D50" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3074,7 +3060,7 @@
       </c>
       <c r="C51" s="6">
         <f>+_xll.YahooQuote(C$1,$B51)</f>
-        <v>208.18</v>
+        <v>284.68</v>
       </c>
       <c r="D51" s="6">
         <f t="shared" si="1"/>
@@ -3083,7 +3069,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3094,7 +3080,7 @@
       </c>
       <c r="C52" s="6">
         <f>+_xll.YahooQuote(C$1,$B52)</f>
-        <v>-7.0007323999999996E-2</v>
+        <v>0.36999512000000001</v>
       </c>
       <c r="D52" s="6">
         <f t="shared" si="1"/>
@@ -3103,7 +3089,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3114,14 +3100,14 @@
       </c>
       <c r="C53" s="6">
         <f>+_xll.YahooQuote(C$1,$B53)</f>
-        <v>-3.3616963999999999E-2</v>
+        <v>0.13013791999999999</v>
       </c>
       <c r="D53" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3139,7 +3125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3157,7 +3143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3175,7 +3161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3193,7 +3179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3204,14 +3190,14 @@
       </c>
       <c r="C58" s="6">
         <f>+_xll.YahooQuote(C$1,$B58)</f>
-        <v>-18000000</v>
+        <v>-14400000</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3231,7 +3217,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="9"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3242,7 +3228,7 @@
       </c>
       <c r="C60" s="6" t="str">
         <f>+_xll.YahooQuote(C$1,$B60)</f>
-        <v>EST</v>
+        <v>EDT</v>
       </c>
       <c r="D60" s="6">
         <f t="shared" si="1"/>
@@ -3251,7 +3237,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="9"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3262,7 +3248,7 @@
       </c>
       <c r="C61" s="6">
         <f>+_xll.YahooQuote(C$1,$B61)</f>
-        <v>45545</v>
+        <v>45910</v>
       </c>
       <c r="D61" s="6">
         <f t="shared" si="1"/>
@@ -3271,7 +3257,7 @@
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3282,7 +3268,7 @@
       </c>
       <c r="C62" s="6">
         <f>+_xll.YahooQuote(C$1,$B62)</f>
-        <v>6.68</v>
+        <v>6.72</v>
       </c>
       <c r="D62" s="6">
         <f t="shared" si="1"/>
@@ -3291,7 +3277,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3302,14 +3288,14 @@
       </c>
       <c r="C63" s="6">
         <f>+_xll.YahooQuote(C$1,$B63)</f>
-        <v>6.66</v>
+        <v>6.69</v>
       </c>
       <c r="D63" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3320,14 +3306,14 @@
       </c>
       <c r="C64" s="6">
         <f>+_xll.YahooQuote(C$1,$B64)</f>
-        <v>3.21</v>
+        <v>2.36</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3338,14 +3324,14 @@
       </c>
       <c r="C65" s="6">
         <f>+_xll.YahooQuote(C$1,$B65)</f>
-        <v>3.2217490000000001E-2</v>
+        <v>2.3770607999999999E-2</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3356,14 +3342,14 @@
       </c>
       <c r="C66" s="6">
         <f>+_xll.YahooQuote(C$1,$B66)</f>
-        <v>20.317074000000002</v>
+        <v>25.495018000000002</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3374,14 +3360,14 @@
       </c>
       <c r="C67" s="6">
         <f>+_xll.YahooQuote(C$1,$B67)</f>
-        <v>10.25</v>
+        <v>11.151590000000001</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3399,7 +3385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69">
         <f t="shared" ref="A69:A105" si="3">+A68+1</f>
         <v>67</v>
@@ -3410,7 +3396,7 @@
       </c>
       <c r="C69" s="6">
         <f>+_xll.YahooQuote(C$1,$B69)</f>
-        <v>6.85</v>
+        <v>6.2</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" si="2"/>
@@ -3419,7 +3405,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="9"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70">
         <f t="shared" si="3"/>
         <v>68</v>
@@ -3430,7 +3416,7 @@
       </c>
       <c r="C70" s="14">
         <f>+_xll.YahooQuote(C$1,$B70)</f>
-        <v>45588.838958333334</v>
+        <v>45952.833333333336</v>
       </c>
       <c r="D70" s="6">
         <f t="shared" si="2"/>
@@ -3439,7 +3425,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="9"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71">
         <f t="shared" si="3"/>
         <v>69</v>
@@ -3450,7 +3436,7 @@
       </c>
       <c r="C71" s="14">
         <f>+_xll.YahooQuote(C$1,$B71)</f>
-        <v>45686.875</v>
+        <v>45952.833333333336</v>
       </c>
       <c r="D71" s="6">
         <f t="shared" si="2"/>
@@ -3459,7 +3445,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72">
         <f t="shared" si="3"/>
         <v>70</v>
@@ -3470,14 +3456,14 @@
       </c>
       <c r="C72" s="14">
         <f>+_xll.YahooQuote(C$1,$B72)</f>
-        <v>45687.875</v>
+        <v>45952.833333333336</v>
       </c>
       <c r="D72" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73">
         <f t="shared" si="3"/>
         <v>71</v>
@@ -3488,7 +3474,7 @@
       </c>
       <c r="C73" s="14">
         <f>+_xll.YahooQuote(C$1,$B73)</f>
-        <v>45588.875</v>
+        <v>45952.875</v>
       </c>
       <c r="D73" s="6">
         <f t="shared" si="2"/>
@@ -3497,7 +3483,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="9"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74">
         <f t="shared" si="3"/>
         <v>72</v>
@@ -3508,14 +3494,14 @@
       </c>
       <c r="C74" s="14">
         <f>+_xll.YahooQuote(C$1,$B74)</f>
-        <v>45588.875</v>
+        <v>45952.875</v>
       </c>
       <c r="D74" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75">
         <f t="shared" si="3"/>
         <v>73</v>
@@ -3526,7 +3512,7 @@
       </c>
       <c r="C75" s="6" t="b">
         <f>+_xll.YahooQuote(C$1,$B75)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" s="6">
         <f t="shared" si="2"/>
@@ -3535,7 +3521,7 @@
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76">
         <f t="shared" si="3"/>
         <v>74</v>
@@ -3555,7 +3541,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77">
         <f t="shared" si="3"/>
         <v>75</v>
@@ -3575,7 +3561,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78">
         <f t="shared" si="3"/>
         <v>76</v>
@@ -3586,7 +3572,7 @@
       </c>
       <c r="C78" s="6">
         <f>+_xll.YahooQuote(C$1,$B78)</f>
-        <v>26.44</v>
+        <v>29.530999999999999</v>
       </c>
       <c r="D78" s="6">
         <f t="shared" si="2"/>
@@ -3595,7 +3581,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79">
         <f t="shared" si="3"/>
         <v>77</v>
@@ -3615,7 +3601,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80">
         <f t="shared" si="3"/>
         <v>78</v>
@@ -3626,7 +3612,7 @@
       </c>
       <c r="C80" s="6">
         <f>+_xll.YahooQuote(C$1,$B80)</f>
-        <v>30.40146</v>
+        <v>45.856453000000002</v>
       </c>
       <c r="D80" s="6">
         <f t="shared" si="2"/>
@@ -3635,7 +3621,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -3646,14 +3632,14 @@
       </c>
       <c r="C81" s="6">
         <f>+_xll.YahooQuote(C$1,$B81)</f>
-        <v>19.62771</v>
+        <v>26.796420000000001</v>
       </c>
       <c r="D81" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82">
         <f t="shared" si="3"/>
         <v>80</v>
@@ -3664,14 +3650,14 @@
       </c>
       <c r="C82" s="6">
         <f>+_xll.YahooQuote(C$1,$B82)</f>
-        <v>7.8763237000000004</v>
+        <v>9.6275099999999991</v>
       </c>
       <c r="D82" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83">
         <f t="shared" si="3"/>
         <v>81</v>
@@ -3689,7 +3675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84">
         <f t="shared" si="3"/>
         <v>82</v>
@@ -3707,7 +3693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85">
         <f t="shared" si="3"/>
         <v>83</v>
@@ -3725,7 +3711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86">
         <f t="shared" si="3"/>
         <v>84</v>
@@ -3743,7 +3729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87">
         <f t="shared" si="3"/>
         <v>85</v>
@@ -3754,14 +3740,14 @@
       </c>
       <c r="C87" s="6">
         <f>+_xll.YahooQuote(C$1,$B87)</f>
-        <v>216.72280000000001</v>
+        <v>254.90100000000001</v>
       </c>
       <c r="D87" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88">
         <f t="shared" si="3"/>
         <v>86</v>
@@ -3772,14 +3758,14 @@
       </c>
       <c r="C88" s="6">
         <f>+_xll.YahooQuote(C$1,$B88)</f>
-        <v>-8.4727940000000004</v>
+        <v>29.408996999999999</v>
       </c>
       <c r="D88" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89">
         <f t="shared" si="3"/>
         <v>87</v>
@@ -3790,14 +3776,14 @@
       </c>
       <c r="C89" s="6">
         <f>+_xll.YahooQuote(C$1,$B89)</f>
-        <v>-3.9095074E-2</v>
+        <v>0.11537419</v>
       </c>
       <c r="D89" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90">
         <f t="shared" si="3"/>
         <v>88</v>
@@ -3808,14 +3794,14 @@
       </c>
       <c r="C90" s="6">
         <f>+_xll.YahooQuote(C$1,$B90)</f>
-        <v>190.2792</v>
+        <v>252.27444</v>
       </c>
       <c r="D90" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91">
         <f t="shared" si="3"/>
         <v>89</v>
@@ -3826,14 +3812,14 @@
       </c>
       <c r="C91" s="6">
         <f>+_xll.YahooQuote(C$1,$B91)</f>
-        <v>17.970794999999999</v>
+        <v>32.035553</v>
       </c>
       <c r="D91" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92">
         <f t="shared" si="3"/>
         <v>90</v>
@@ -3844,14 +3830,14 @@
       </c>
       <c r="C92" s="6">
         <f>+_xll.YahooQuote(C$1,$B92)</f>
-        <v>9.4444340000000002E-2</v>
+        <v>0.12698690000000001</v>
       </c>
       <c r="D92" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93">
         <f t="shared" si="3"/>
         <v>91</v>
@@ -3862,14 +3848,14 @@
       </c>
       <c r="C93" s="6">
         <f>+_xll.YahooQuote(C$1,$B93)</f>
-        <v>39.793239999999997</v>
+        <v>28.600501999999999</v>
       </c>
       <c r="D93" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94">
         <f t="shared" si="3"/>
         <v>92</v>
@@ -3880,14 +3866,14 @@
       </c>
       <c r="C94" s="6">
         <f>+_xll.YahooQuote(C$1,$B94)</f>
-        <v>237.37</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="D94" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95">
         <f t="shared" si="3"/>
         <v>93</v>
@@ -3898,14 +3884,14 @@
       </c>
       <c r="C95" s="6">
         <f>+_xll.YahooQuote(C$1,$B95)</f>
-        <v>-29.119994999999999</v>
+        <v>-11.850006</v>
       </c>
       <c r="D95" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96">
         <f t="shared" si="3"/>
         <v>94</v>
@@ -3916,14 +3902,14 @@
       </c>
       <c r="C96" s="6">
         <f>+_xll.YahooQuote(C$1,$B96)</f>
-        <v>-0.12267765999999999</v>
+        <v>-4.0012177000000003E-2</v>
       </c>
       <c r="D96" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97">
         <f t="shared" si="3"/>
         <v>95</v>
@@ -3934,14 +3920,14 @@
       </c>
       <c r="C97" s="6">
         <f>+_xll.YahooQuote(C$1,$B97)</f>
-        <v>145.28</v>
+        <v>203.51</v>
       </c>
       <c r="D97" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98">
         <f t="shared" si="3"/>
         <v>96</v>
@@ -3952,14 +3938,14 @@
       </c>
       <c r="C98" s="6">
         <f>+_xll.YahooQuote(C$1,$B98)</f>
-        <v>62.97</v>
+        <v>80.8</v>
       </c>
       <c r="D98" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99">
         <f t="shared" si="3"/>
         <v>97</v>
@@ -3970,14 +3956,14 @@
       </c>
       <c r="C99" s="6">
         <f>+_xll.YahooQuote(C$1,$B99)</f>
-        <v>0.43343890000000002</v>
+        <v>0.3970321</v>
       </c>
       <c r="D99" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100">
         <f t="shared" si="3"/>
         <v>98</v>
@@ -3988,14 +3974,14 @@
       </c>
       <c r="C100" s="6" t="str">
         <f>+_xll.YahooQuote(C$1,$B100)</f>
-        <v>145.28 - 237.37</v>
+        <v>203.51 - 296.16</v>
       </c>
       <c r="D100" s="6">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101">
         <f t="shared" si="3"/>
         <v>99</v>
@@ -4006,14 +3992,14 @@
       </c>
       <c r="C101" s="6" t="str">
         <f>+_xll.YahooQuote(C$1,$B101)</f>
-        <v>2.6 - Hold</v>
+        <v>2.5 - Hold</v>
       </c>
       <c r="D101" s="6">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102">
         <f t="shared" si="3"/>
         <v>100</v>
@@ -4031,7 +4017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103">
         <f t="shared" si="3"/>
         <v>101</v>
@@ -4049,7 +4035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104">
         <f t="shared" si="3"/>
         <v>102</v>
@@ -4067,7 +4053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -4094,20 +4080,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC0A5A9-4647-4C7E-A8C9-53414205A4D9}">
   <dimension ref="A2:K11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="36.36328125" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="10.84375" customWidth="1"/>
+    <col min="2" max="2" width="36.3828125" customWidth="1"/>
+    <col min="5" max="5" width="10.61328125" customWidth="1"/>
+    <col min="6" max="6" width="17.84375" style="11" customWidth="1"/>
     <col min="7" max="7" width="11" style="13" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" style="13" customWidth="1"/>
-    <col min="9" max="9" width="19.36328125" customWidth="1"/>
+    <col min="8" max="8" width="11.4609375" style="13" customWidth="1"/>
+    <col min="9" max="9" width="19.3828125" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="26.54296875" customWidth="1"/>
+    <col min="11" max="11" width="26.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4142,7 +4128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -4164,36 +4150,36 @@
       </c>
       <c r="F3" s="11">
         <f>_xll.YahooQuote($A3,F$2)</f>
-        <v>248.98</v>
+        <v>440.4</v>
       </c>
       <c r="G3" s="13">
         <f>_xll.YahooQuote($A3,G$2)</f>
-        <v>248.94</v>
+        <v>415.63</v>
       </c>
       <c r="H3" s="13">
         <f>_xll.YahooQuote($A3,H$2)</f>
-        <v>249.08</v>
+        <v>458.7</v>
       </c>
       <c r="I3" s="4">
         <f>_xll.YahooQuote($A3,I$2)</f>
-        <v>799240749056</v>
+        <v>1464396414976</v>
       </c>
       <c r="J3" s="4">
         <f>_xll.YahooQuote($A3,J$2)*F3</f>
-        <v>13973893695.74</v>
+        <v>44099634564</v>
       </c>
       <c r="K3" s="5">
         <f>_xll.YahooQuote($A3,K$2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="str">
         <f>_xll.YahooQuote($A4,B$2)</f>
-        <v>SPDR S&amp;P 500 ETF Trust</v>
+        <v>SPDR S&amp;P 500 ETF</v>
       </c>
       <c r="C4" t="str">
         <f>_xll.YahooQuote($A4,C$2)</f>
@@ -4209,30 +4195,30 @@
       </c>
       <c r="F4" s="11">
         <f>_xll.YahooQuote($A4,F$2)</f>
-        <v>571.04</v>
+        <v>661.82</v>
       </c>
       <c r="G4" s="13">
         <f>_xll.YahooQuote($A4,G$2)</f>
-        <v>571.29999999999995</v>
+        <v>662.05</v>
       </c>
       <c r="H4" s="13">
         <f>_xll.YahooQuote($A4,H$2)</f>
-        <v>571.39</v>
+        <v>662.19</v>
       </c>
       <c r="I4" s="4">
         <f>_xll.YahooQuote($A4,I$2)</f>
-        <v>524090212352</v>
+        <v>607406522368</v>
       </c>
       <c r="J4" s="4">
         <f>_xll.YahooQuote($A4,J$2)*F4</f>
-        <v>25513556119.199997</v>
+        <v>40009783422.139999</v>
       </c>
       <c r="K4" s="5">
         <f>_xll.YahooQuote($A4,K$2)</f>
-        <v>9.9570909999999995E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>8.6042099999999993E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -4254,30 +4240,30 @@
       </c>
       <c r="F5" s="11">
         <f>_xll.YahooQuote($A5,F$2)</f>
-        <v>36.770000000000003</v>
+        <v>44.34</v>
       </c>
       <c r="G5" s="13">
         <f>_xll.YahooQuote($A5,G$2)</f>
-        <v>36.770000000000003</v>
+        <v>44.3</v>
       </c>
       <c r="H5" s="13">
         <f>_xll.YahooQuote($A5,H$2)</f>
-        <v>36.79</v>
+        <v>44.44</v>
       </c>
       <c r="I5" s="4">
         <f>_xll.YahooQuote($A5,I$2)</f>
-        <v>12957748224</v>
+        <v>15625415680</v>
       </c>
       <c r="J5" s="4">
         <f>_xll.YahooQuote($A5,J$2)*F5</f>
-        <v>68948419.790000007</v>
+        <v>83207557.200000003</v>
       </c>
       <c r="K5" s="5">
         <f>_xll.YahooQuote($A5,K$2)</f>
-        <v>1.6362150999999998E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>1.3528749E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4299,15 +4285,15 @@
       </c>
       <c r="F6" s="11">
         <f>_xll.YahooQuote($A6,F$2)</f>
-        <v>2773</v>
+        <v>3306</v>
       </c>
       <c r="G6" s="13">
         <f>_xll.YahooQuote($A6,G$2)</f>
-        <v>2769</v>
+        <v>3306</v>
       </c>
       <c r="H6" s="13">
         <f>_xll.YahooQuote($A6,H$2)</f>
-        <v>2773</v>
+        <v>3314</v>
       </c>
       <c r="I6" s="4" t="str">
         <f>_xll.YahooQuote($A6,I$2)</f>
@@ -4315,14 +4301,14 @@
       </c>
       <c r="J6" s="4">
         <f>_xll.YahooQuote($A6,J$2)*F6</f>
-        <v>3972377960</v>
+        <v>6567666540</v>
       </c>
       <c r="K6" s="5" t="str">
         <f>_xll.YahooQuote($A6,K$2)</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4344,15 +4330,15 @@
       </c>
       <c r="F7" s="11">
         <f>_xll.YahooQuote($A7,F$2)</f>
-        <v>69.33</v>
+        <v>65.72</v>
       </c>
       <c r="G7" s="13">
         <f>_xll.YahooQuote($A7,G$2)</f>
-        <v>69.319999999999993</v>
+        <v>65.16</v>
       </c>
       <c r="H7" s="13">
         <f>_xll.YahooQuote($A7,H$2)</f>
-        <v>69.349999999999994</v>
+        <v>65.2</v>
       </c>
       <c r="I7" s="4" t="str">
         <f>_xll.YahooQuote($A7,I$2)</f>
@@ -4360,14 +4346,14 @@
       </c>
       <c r="J7" s="4">
         <f>_xll.YahooQuote($A7,J$2)*F7</f>
-        <v>20347731.030000001</v>
+        <v>17528641.239999998</v>
       </c>
       <c r="K7" s="5" t="str">
         <f>_xll.YahooQuote($A7,K$2)</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -4389,15 +4375,15 @@
       </c>
       <c r="F8" s="11">
         <f>_xll.YahooQuote($A8,F$2)</f>
-        <v>1.0837759</v>
+        <v>1.1708231</v>
       </c>
       <c r="G8" s="13">
         <f>_xll.YahooQuote($A8,G$2)</f>
-        <v>1.0837759</v>
+        <v>1.1708231</v>
       </c>
       <c r="H8" s="13">
         <f>_xll.YahooQuote($A8,H$2)</f>
-        <v>1.0831888999999999</v>
+        <v>1.1701379999999999</v>
       </c>
       <c r="I8" s="4" t="str">
         <f>_xll.YahooQuote($A8,I$2)</f>
@@ -4412,13 +4398,13 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I11" s="4"/>
     </row>
   </sheetData>
